--- a/materials/03_한글표만들기/4반_명렬표.xlsx
+++ b/materials/03_한글표만들기/4반_명렬표.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>홍길동1</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>홍길동2</t>
+          <t>김서연</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>홍길동3</t>
+          <t>이서준</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>홍길동4</t>
+          <t>이하은</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>홍길동5</t>
+          <t>박하준</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>홍길동6</t>
+          <t>박지유</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>홍길동7</t>
+          <t>최은우</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>홍길동8</t>
+          <t>최수아</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>홍길동9</t>
+          <t>정시우</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>홍길동10</t>
+          <t>정하린</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>홍길동11</t>
+          <t>조유준</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>홍길동12</t>
+          <t>조채원</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>홍길동13</t>
+          <t>장예준</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>홍길동14</t>
+          <t>황지아</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>홍길동15</t>
+          <t>임주원</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>홍길동16</t>
+          <t>안소율</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>홍길동17</t>
+          <t>신지호</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>홍길동18</t>
+          <t>유다은</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>홍길동19</t>
+          <t>백승현</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>홍길동20</t>
+          <t>고윤아</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>홍길동21</t>
+          <t>전준서</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>홍길동22</t>
+          <t>차서아</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>홍길동23</t>
+          <t>송민재</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>홍길동24</t>
+          <t>양예린</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>홍길동25</t>
+          <t>노우진</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>홍길동26</t>
+          <t>허나윤</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
